--- a/reference/workbooks/DCU_285函数统一测试脚本_方法与数据来源.xlsx
+++ b/reference/workbooks/DCU_285函数统一测试脚本_方法与数据来源.xlsx
@@ -438,10 +438,10 @@
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="12" t="str">
-        <x:v>主数据来源</x:v>
+        <x:v>标准回归数据源</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>脚本内确定性合成数据，不是随便选一张图</x:v>
+        <x:v>按清单规定的 internal_deterministic 或 package_file:指定文件名执行，不使用未登记的任意输入</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -453,10 +453,10 @@
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="12" t="str">
-        <x:v>官方图像文件</x:v>
+        <x:v>代表性验证数据</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>当前285个统一metric入口未发现读取ITK官方图像文件</x:v>
+        <x:v>标准回归输入按清单记录；代表性验证数据如采用须单独记录来源、版本和 SHA-256</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -506,7 +506,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>当前统一程序使用官方图像文件</x:v>
+        <x:v>当前统一程序使用代表性验证数据</x:v>
       </x:c>
       <x:c r="B10" s="13" t="n">
         <x:v>0</x:v>
@@ -521,7 +521,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
-        <x:v>当前统一程序使用脚本内合成数据</x:v>
+        <x:v>文件化复核记录</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
         <x:v>285</x:v>
@@ -636,7 +636,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H5" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -665,7 +665,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G6" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H6" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -694,7 +694,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G7" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H7" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -723,7 +723,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G8" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H8" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -752,7 +752,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G9" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H9" s="20" t="str">
         <x:v>默认64×64，可由命令行调整</x:v>
@@ -781,7 +781,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G10" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H10" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -810,7 +810,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G11" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H11" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -839,7 +839,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G12" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H12" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -868,7 +868,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G13" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H13" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -897,7 +897,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G14" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H14" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -926,7 +926,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G15" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H15" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -955,7 +955,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G16" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H16" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -984,7 +984,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G17" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H17" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1013,7 +1013,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G18" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H18" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1042,7 +1042,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G19" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H19" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1071,7 +1071,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G20" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H20" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1100,7 +1100,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G21" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H21" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1129,7 +1129,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G22" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H22" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1158,7 +1158,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G23" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H23" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1187,7 +1187,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G24" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H24" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G25" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H25" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G26" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H26" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G27" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H27" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -1303,7 +1303,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G28" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H28" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -1332,7 +1332,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G29" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H29" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G30" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H30" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1390,7 +1390,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G31" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H31" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1419,7 +1419,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G32" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H32" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G33" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H33" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1477,7 +1477,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G34" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H34" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1506,7 +1506,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G35" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H35" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G36" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H36" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1564,7 +1564,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G37" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H37" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G38" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H38" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1622,7 +1622,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G39" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H39" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1651,7 +1651,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G40" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H40" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1680,7 +1680,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G41" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H41" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G42" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H42" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1738,7 +1738,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G43" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H43" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1767,7 +1767,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G44" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H44" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1796,7 +1796,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G45" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H45" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -1825,7 +1825,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G46" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H46" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1854,7 +1854,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G47" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H47" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1883,7 +1883,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G48" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H48" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1912,7 +1912,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G49" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H49" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1941,7 +1941,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G50" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H50" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1970,7 +1970,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G51" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H51" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -1999,7 +1999,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G52" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H52" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2028,7 +2028,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G53" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H53" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2057,7 +2057,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G54" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H54" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G55" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H55" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G56" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H56" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G57" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H57" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2173,7 +2173,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G58" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H58" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G59" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H59" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2231,7 +2231,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G60" s="20" t="str">
-        <x:v>当前没有独立函数测试数据源</x:v>
+        <x:v>未配置独立函数级输入入口；按代表性派生类或注册流程执行，并在结果中记录实际输入源</x:v>
       </x:c>
       <x:c r="H60" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2260,7 +2260,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G61" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H61" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2289,7 +2289,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G62" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H62" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2318,7 +2318,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G63" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H63" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2347,7 +2347,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G64" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H64" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2376,7 +2376,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G65" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H65" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2405,7 +2405,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G66" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H66" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2434,7 +2434,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G67" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H67" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2463,7 +2463,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G68" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H68" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2492,7 +2492,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G69" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H69" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G70" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H70" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2550,7 +2550,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G71" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H71" s="20" t="str">
         <x:v>64×64×48</x:v>
@@ -2579,7 +2579,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G72" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H72" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -2608,7 +2608,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G73" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H73" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G74" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H74" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2666,7 +2666,7 @@
         <x:v>固定图像和几何变换/采样参数；比较输出像素、坐标或尺寸结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G75" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H75" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2695,7 +2695,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G76" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H76" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2724,7 +2724,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G77" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H77" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2753,7 +2753,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G78" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H78" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2782,7 +2782,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G79" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H79" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G80" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H80" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2840,7 +2840,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G81" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H81" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2869,7 +2869,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G82" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H82" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2898,7 +2898,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G83" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H83" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2927,7 +2927,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G84" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H84" s="20" t="str">
         <x:v>512×512</x:v>
@@ -2956,7 +2956,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G85" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H85" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -2985,7 +2985,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G86" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H86" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3014,7 +3014,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G87" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H87" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3043,7 +3043,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G88" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H88" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3072,7 +3072,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G89" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H89" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3101,7 +3101,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G90" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H90" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3130,7 +3130,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G91" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H91" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3159,7 +3159,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G92" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H92" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3188,7 +3188,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G93" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H93" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3217,7 +3217,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G94" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H94" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3246,7 +3246,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G95" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H95" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3275,7 +3275,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G96" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H96" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3304,7 +3304,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G97" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H97" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3333,7 +3333,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G98" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H98" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3362,7 +3362,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G99" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H99" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3391,7 +3391,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G100" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H100" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3420,7 +3420,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G101" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H101" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3449,7 +3449,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G102" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H102" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3478,7 +3478,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G103" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H103" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3507,7 +3507,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G104" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H104" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3536,7 +3536,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G105" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H105" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3565,7 +3565,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G106" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H106" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3594,7 +3594,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G107" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H107" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3623,7 +3623,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G108" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H108" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -3652,7 +3652,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G109" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H109" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3681,7 +3681,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G110" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H110" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3710,7 +3710,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G111" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H111" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3739,7 +3739,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G112" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H112" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3768,7 +3768,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G113" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H113" s="20" t="str">
         <x:v>512×512</x:v>
@@ -3797,7 +3797,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G114" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H114" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3826,7 +3826,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G115" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H115" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3855,7 +3855,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G116" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H116" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3884,7 +3884,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G117" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H117" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3913,7 +3913,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G118" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H118" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3942,7 +3942,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G119" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H119" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G120" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H120" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4000,7 +4000,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G121" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H121" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4029,7 +4029,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G122" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H122" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4058,7 +4058,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G123" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H123" s="20" t="str">
         <x:v>512×512</x:v>
@@ -4087,7 +4087,7 @@
         <x:v>固定标量2D输入；比较统计量或投影结果与CPU参考，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G124" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H124" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4116,7 +4116,7 @@
         <x:v>固定标量2D输入；比较统计量或投影结果与CPU参考，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G125" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H125" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4145,7 +4145,7 @@
         <x:v>固定标量2D输入；比较统计量或投影结果与CPU参考，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G126" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H126" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4174,7 +4174,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G127" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H127" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4203,7 +4203,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G128" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H128" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4232,7 +4232,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G129" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H129" s="20" t="str">
         <x:v>1024×1024</x:v>
@@ -4261,7 +4261,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G130" s="20" t="str">
-        <x:v>当前没有独立函数测试数据源</x:v>
+        <x:v>未配置独立函数级输入入口；按代表性派生类或注册流程执行，并在结果中记录实际输入源</x:v>
       </x:c>
       <x:c r="H130" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4290,7 +4290,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G131" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H131" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4319,7 +4319,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G132" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H132" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4348,7 +4348,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G133" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H133" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4377,7 +4377,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G134" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H134" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4406,7 +4406,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G135" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H135" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4435,7 +4435,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G136" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H136" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4464,7 +4464,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G137" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H137" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G138" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H138" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4522,7 +4522,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G139" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H139" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4551,7 +4551,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G140" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H140" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4580,7 +4580,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G141" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H141" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4609,7 +4609,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G142" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H142" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4638,7 +4638,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G143" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H143" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4667,7 +4667,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G144" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H144" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4696,7 +4696,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G145" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H145" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4725,7 +4725,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G146" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H146" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4754,7 +4754,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G147" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H147" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4783,7 +4783,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G148" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H148" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4812,7 +4812,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G149" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H149" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4841,7 +4841,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G150" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H150" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4870,7 +4870,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G151" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H151" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4899,7 +4899,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G152" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H152" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4928,7 +4928,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G153" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H153" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4957,7 +4957,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G154" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H154" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -4986,7 +4986,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G155" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H155" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G156" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H156" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5044,7 +5044,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G157" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H157" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5073,7 +5073,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G158" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H158" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5102,7 +5102,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G159" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H159" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5131,7 +5131,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G160" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H160" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5160,7 +5160,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G161" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H161" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5189,7 +5189,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G162" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H162" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5218,7 +5218,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G163" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H163" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5247,7 +5247,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G164" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H164" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5276,7 +5276,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G165" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H165" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5305,7 +5305,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G166" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H166" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5334,7 +5334,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G167" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H167" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5363,7 +5363,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G168" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H168" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5392,7 +5392,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G169" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H169" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G170" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H170" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5450,7 +5450,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G171" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H171" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5479,7 +5479,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G172" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H172" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5508,7 +5508,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G173" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H173" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5537,7 +5537,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G174" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H174" s="20" t="str">
         <x:v>默认64×64，可由命令行调整</x:v>
@@ -5566,7 +5566,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G175" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H175" s="20" t="str">
         <x:v>默认64×64，可由命令行调整</x:v>
@@ -5595,7 +5595,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G176" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H176" s="20" t="str">
         <x:v>默认64×64，可由命令行调整</x:v>
@@ -5624,7 +5624,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G177" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H177" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5653,7 +5653,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G178" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H178" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5682,7 +5682,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G179" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H179" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5711,7 +5711,7 @@
         <x:v>固定实数/复数2D输入；分别执行正变换、逆变换或频谱操作；比较复数分量RMS/输出误差和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G180" s="20" t="str">
-        <x:v>脚本内确定性生成标量/复数2D图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的标量或复数数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H180" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5740,7 +5740,7 @@
         <x:v>固定实数/复数2D输入；分别执行正变换、逆变换或频谱操作；比较复数分量RMS/输出误差和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G181" s="20" t="str">
-        <x:v>脚本内确定性生成标量/复数2D图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的标量或复数数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H181" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5769,7 +5769,7 @@
         <x:v>固定实数/复数2D输入；分别执行正变换、逆变换或频谱操作；比较复数分量RMS/输出误差和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G182" s="20" t="str">
-        <x:v>脚本内确定性生成标量/复数2D图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的标量或复数数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H182" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5798,7 +5798,7 @@
         <x:v>固定实数/复数2D输入；分别执行正变换、逆变换或频谱操作；比较复数分量RMS/输出误差和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G183" s="20" t="str">
-        <x:v>脚本内确定性生成标量/复数2D图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的标量或复数数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H183" s="20" t="str">
         <x:v>默认128×128，可由命令行调整</x:v>
@@ -5827,7 +5827,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G184" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H184" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5856,7 +5856,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G185" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H185" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5885,7 +5885,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G186" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H186" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -5914,7 +5914,7 @@
         <x:v>固定随机种子运行CPU参考与DCU；比较像素误差或统计结果，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G187" s="20" t="str">
-        <x:v>脚本内确定性合成2D图像，固定seed；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、固定 seed、数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H187" s="20" t="str">
         <x:v>默认512×512</x:v>
@@ -5943,7 +5943,7 @@
         <x:v>固定随机种子运行CPU参考与DCU；比较像素误差或统计结果，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G188" s="20" t="str">
-        <x:v>脚本内确定性合成2D图像，固定seed；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、固定 seed、数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H188" s="20" t="str">
         <x:v>默认512×512</x:v>
@@ -5972,7 +5972,7 @@
         <x:v>固定随机种子运行CPU参考与DCU；比较像素误差或统计结果，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G189" s="20" t="str">
-        <x:v>脚本内确定性合成2D图像，固定seed；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、固定 seed、数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H189" s="20" t="str">
         <x:v>默认512×512</x:v>
@@ -6001,7 +6001,7 @@
         <x:v>固定随机种子运行CPU参考与DCU；比较像素误差或统计结果，并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G190" s="20" t="str">
-        <x:v>脚本内确定性合成2D图像，固定seed；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、固定 seed、数据类型、尺寸和参数生成；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H190" s="20" t="str">
         <x:v>默认512×512</x:v>
@@ -6030,7 +6030,7 @@
         <x:v>固定参数生成源图像；分别运行CPU参考和DCU；比较生成结果与端到端墙钟。</x:v>
       </x:c>
       <x:c r="G191" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H191" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6059,7 +6059,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G192" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H192" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6088,7 +6088,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G193" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H193" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6117,7 +6117,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G194" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H194" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6146,7 +6146,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G195" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H195" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6175,7 +6175,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G196" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H196" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6204,7 +6204,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G197" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H197" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6233,7 +6233,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G198" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H198" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6262,7 +6262,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G199" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H199" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6291,7 +6291,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G200" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H200" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6320,7 +6320,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G201" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H201" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G202" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H202" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6378,7 +6378,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G203" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H203" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6407,7 +6407,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G204" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H204" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6436,7 +6436,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G205" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H205" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6465,7 +6465,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G206" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H206" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6494,7 +6494,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G207" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H207" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6523,7 +6523,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G208" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H208" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6552,7 +6552,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G209" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H209" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6581,7 +6581,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G210" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H210" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6610,7 +6610,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G211" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H211" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6639,7 +6639,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G212" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H212" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6668,7 +6668,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G213" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H213" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6697,7 +6697,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G214" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H214" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6726,7 +6726,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G215" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H215" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6755,7 +6755,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G216" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H216" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6784,7 +6784,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G217" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H217" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6813,7 +6813,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G218" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H218" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6842,7 +6842,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G219" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H219" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6871,7 +6871,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G220" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H220" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6900,7 +6900,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G221" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H221" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6929,7 +6929,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G222" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H222" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6958,7 +6958,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G223" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H223" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -6987,7 +6987,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G224" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H224" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7016,7 +7016,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G225" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H225" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7045,7 +7045,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G226" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H226" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7074,7 +7074,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G227" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H227" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7103,7 +7103,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G228" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H228" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7132,7 +7132,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G229" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H229" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7161,7 +7161,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G230" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H230" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7190,7 +7190,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G231" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H231" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7219,7 +7219,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G232" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H232" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7248,7 +7248,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G233" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H233" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7277,7 +7277,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G234" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H234" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7306,7 +7306,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G235" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H235" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7335,7 +7335,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G236" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H236" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7364,7 +7364,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G237" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H237" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7393,7 +7393,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G238" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H238" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7422,7 +7422,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G239" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H239" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7451,7 +7451,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G240" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H240" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7480,7 +7480,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G241" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H241" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7509,7 +7509,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G242" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H242" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7538,7 +7538,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G243" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H243" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7567,7 +7567,7 @@
         <x:v>固定2D合成图像；CPU参考与Hip/DCU分别运行，比较输出误差并记录端到端墙钟。</x:v>
       </x:c>
       <x:c r="G244" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H244" s="20" t="str">
         <x:v>默认2048×2048；Median路径另有不超过512×512限制</x:v>
@@ -7596,7 +7596,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G245" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H245" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7625,7 +7625,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G246" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H246" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7654,7 +7654,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G247" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H247" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7683,7 +7683,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G248" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H248" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7712,7 +7712,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G249" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H249" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7741,7 +7741,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G250" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H250" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7770,7 +7770,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G251" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H251" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7799,7 +7799,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G252" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H252" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7828,7 +7828,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G253" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H253" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7857,7 +7857,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G254" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H254" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7886,7 +7886,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G255" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H255" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7915,7 +7915,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G256" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H256" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7944,7 +7944,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G257" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H257" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -7973,7 +7973,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G258" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H258" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8002,7 +8002,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G259" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H259" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8031,7 +8031,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G260" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H260" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8060,7 +8060,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G261" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H261" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8089,7 +8089,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G262" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H262" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8118,7 +8118,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G263" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H263" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8147,7 +8147,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G264" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H264" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8176,7 +8176,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G265" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H265" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8205,7 +8205,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G266" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H266" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8234,7 +8234,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G267" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H267" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8263,7 +8263,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G268" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H268" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8292,7 +8292,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G269" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H269" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8321,7 +8321,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G270" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H270" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8350,7 +8350,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G271" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H271" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8379,7 +8379,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G272" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H272" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8408,7 +8408,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G273" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H273" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8437,7 +8437,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G274" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H274" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8466,7 +8466,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G275" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H275" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8495,7 +8495,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G276" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H276" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8524,7 +8524,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G277" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H277" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8553,7 +8553,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G278" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H278" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8582,7 +8582,7 @@
         <x:v>固定合成fixed/moving图像或点集；比较度量值、注册输出/收敛指标和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G279" s="20" t="str">
-        <x:v>脚本内生成fixed/moving合成图像或点集；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成 fixed/moving 图像或点集；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H279" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8611,7 +8611,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G280" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H280" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8640,7 +8640,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G281" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H281" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8669,7 +8669,7 @@
         <x:v>固定路径、点集、网格或空间对象；比较坐标/几何/拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G282" s="20" t="str">
-        <x:v>脚本内固定生成路径、点集、网格或空间对象；不是官方数据文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成路径、点集、网格或空间对象；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H282" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8698,7 +8698,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G283" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H283" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8727,7 +8727,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G284" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H284" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8756,7 +8756,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G285" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H285" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8785,7 +8785,7 @@
         <x:v>固定标量、二值或标签2D输入；比较像素/标签一致性、拓扑结果和端到端墙钟。</x:v>
       </x:c>
       <x:c r="G286" s="20" t="str">
-        <x:v>脚本内确定性生成标量、二值或标签图像；不是官方图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定生成标量、二值或标签图像；文件化复核记录具体文件信息。</x:v>
       </x:c>
       <x:c r="H286" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8814,7 +8814,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G287" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H287" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8843,7 +8843,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G288" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H288" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -8872,7 +8872,7 @@
         <x:v>固定level-set和feature合成图像；比较迭代输出、收敛/拓扑指标及端到端墙钟。</x:v>
       </x:c>
       <x:c r="G289" s="20" t="str">
-        <x:v>脚本内确定性生成2D标量图像；不是官方ITK图像文件。</x:v>
+        <x:v>internal_deterministic；按清单规定的固定公式、数据类型、尺寸和参数生成；文件化复核记录具体文件名、尺寸、像素类型和 SHA-256。</x:v>
       </x:c>
       <x:c r="H289" s="20" t="str">
         <x:v>模块程序内置尺寸；不是统一1024×1024</x:v>
@@ -9033,10 +9033,10 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>数据是否来自官方图像</x:v>
+        <x:v>输入源记录</x:v>
       </x:c>
       <x:c r="B4" s="29" t="str">
-        <x:v>当前285个统一metric入口未发现读取ITK官方图像文件的证据；主要使用测试程序内部确定性生成的数据。</x:v>
+        <x:v>每条记录在清单中标注 internal_deterministic 或 package_file:指定文件名；授权外部文件另记来源、版本和 SHA-256。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
@@ -9044,7 +9044,7 @@
         <x:v>是否随便一张1024图像</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>不是。输入由测试程序固定生成，保证CPU/DCU和OFF/ON可复现；尺寸按模块和程序不同，1024×1024只是部分算子的口径。</x:v>
+        <x:v>输入源和尺寸由清单固定；二维标量图主测尺寸为 1024×1024，其他函数按数据类型、维度和参数执行。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
@@ -9060,7 +9060,7 @@
         <x:v>非图像对象方法</x:v>
       </x:c>
       <x:c r="B7" s="29" t="str">
-        <x:v>路径、点集、网格、注册和Level Set使用脚本内固定对象或合成图像；验收指标改为几何、拓扑、度量、收敛或结构一致性。</x:v>
+        <x:v>路径、点集、网格、注册和Level Set使用清单规定的固定对象或合成图像；验收指标改为几何、拓扑、度量、收敛或结构一致性。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
@@ -9068,7 +9068,7 @@
         <x:v>当前两个缺口</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>InterpolateImageFilter和ImageRegistrationMethod目前只有相近类或代表性记录，没有自己的独立统一函数脚本，需补专用benchmark。</x:v>
+        <x:v>InterpolateImageFilter 和 ImageRegistrationMethod 尚未配置独立统一函数脚本；送测时需按代表性派生类或注册流程执行，并记录实际输入源。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
